--- a/practice/answers/s1_q16.xlsx
+++ b/practice/answers/s1_q16.xlsx
@@ -521,7 +521,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Sandhill</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
@@ -531,7 +531,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Tamarack</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
@@ -541,7 +541,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Upland</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
@@ -551,7 +551,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Verdant</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -561,7 +561,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Rented</t>
+          <t>Westgate</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">

--- a/practice/answers/s1_q16.xlsx
+++ b/practice/answers/s1_q16.xlsx
@@ -482,10 +482,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
@@ -600,18 +600,77 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>7,675 against 15,350. The total row already holds the five fields, so including it adds the whole farm a second time. Leave a blank row under a table, or look at what the range highlights before pressing Enter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Two fields added later</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Xena</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Yardley</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>The original five-row SUM</t>
+        </is>
+      </c>
+      <c r="C18" s="10">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="D18" s="9">
+        <f>_xlfn.FORMULATEXT(C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>SUM over all seven</t>
+        </is>
+      </c>
+      <c r="C19" s="10">
+        <f>SUM(B5:B9,B15:B16)</f>
+        <v/>
+      </c>
+      <c r="D19" s="9">
+        <f>_xlfn.FORMULATEXT(C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>7,675 / 15,350 / 7,675 / 10,230. A range can reach too far and swallow the total row, doubling the answer, or fall short and miss rows added later. Neither raises an error -- both just return a plausible number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q16.xlsx
+++ b/practice/answers/s1_q16.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,45 +26,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -73,12 +38,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,29 +74,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,195 +460,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Summing a range that contains its own total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The second SUM reaches over the total row, so every bushel is counted twice. The giveaway is that the answer is exactly double.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Bushels</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Sandhill</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B2" s="2" t="n">
         <v>1240</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Tamarack</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B3" s="2" t="n">
         <v>2180</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Upland</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B4" s="2" t="n">
         <v>860</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Verdant</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B5" s="2" t="n">
         <v>1975</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Westgate</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>SUM(B2:B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Westgate</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>SUM(B5:B9)</f>
+          <t>SUM including the total row</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>SUM(B2:B7)</f>
         <v/>
       </c>
-      <c r="C10" s="9">
-        <f>_xlfn.FORMULATEXT(B10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>SUM including the total row</t>
-        </is>
-      </c>
-      <c r="C12" s="10">
-        <f>SUM(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="D12" s="9">
-        <f>_xlfn.FORMULATEXT(C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Two fields added later</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Xena</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Yardley</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>The original five-row SUM</t>
-        </is>
-      </c>
-      <c r="C18" s="10">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="D18" s="9">
-        <f>_xlfn.FORMULATEXT(C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>SUM over all seven</t>
-        </is>
-      </c>
-      <c r="C19" s="10">
-        <f>SUM(B5:B9,B15:B16)</f>
-        <v/>
-      </c>
-      <c r="D19" s="9">
-        <f>_xlfn.FORMULATEXT(C19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1"/>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>7,675 / 15,350 / 7,675 / 10,230. A range can reach too far and swallow the total row, doubling the answer, or fall short and miss rows added later. Neither raises an error -- both just return a plausible number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>The total row already holds the sum of the five fields. Including it adds every bushel a second time, so the answer is exactly double.</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>With Xena (1,615) and Yardley (940) typed in below the last row, the original =SUM(B2:B6) still reads 7,675. It was written for five rows and does not widen when rows are added below it, so the two new fields are simply missing. The true total is 10,230 -- a shortfall of 2,555 bushels that nothing on the sheet flags. The sheet here keeps the original five fields.</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>A range can reach too far and swallow a subtotal, doubling the answer, or fall short and miss rows added later. Both return a plausible number with no error. Check what the range actually highlights before pressing Enter, and check it again after the sheet grows.</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:D21"/>
+  <mergeCells count="3">
+    <mergeCell ref="A19:G21"/>
+    <mergeCell ref="A14:G17"/>
+    <mergeCell ref="A11:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
